--- a/ReinsurancePortfolio/TestPlans/ReadMe.xlsx
+++ b/ReinsurancePortfolio/TestPlans/ReadMe.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ARAPL_USER\Desktop\Tests\ReinsurancePortfolio\TestPlans\SupportingData\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52E62D6E-C7D9-4D22-AB13-59A9ACB94607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF16CA81-2EF2-4EFC-8CC3-A7B8C321B220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="190">
   <si>
     <t>Testing Documentation Register</t>
   </si>
@@ -304,18 +304,9 @@
     <t>TPL-003</t>
   </si>
   <si>
-    <t>Macro enabled Microsoft excel to extract Portfolio Metrics from SQL db for the listed ReportIDs</t>
-  </si>
-  <si>
-    <t>ReinsurancePortfolio/TestPlans/SupportingData/Template/BPM00 PortfolioMetrics_Driver.xlsm</t>
-  </si>
-  <si>
     <t>TPL-004</t>
   </si>
   <si>
-    <t>Macro enabled Microsoft excel to extract deal Level AAL and Peril Region AAL for the list of ILS instruments given in the input file and write it to any excel file where the output is required</t>
-  </si>
-  <si>
     <t>ReinsurancePortfolio/TestPlans/SupportingData/Template/PreReq 00 AAL_by_Deal_PerilRegion.xlsm</t>
   </si>
   <si>
@@ -403,9 +394,6 @@
     <t>ReinsurancePortfolio/TestPlans/SupportingData/Template/Pricing 01 Pricing_TestCases.xlsx</t>
   </si>
   <si>
-    <t>Pricing 01 Pricing_TestCases</t>
-  </si>
-  <si>
     <t>Test case scenarios for Pricing</t>
   </si>
   <si>
@@ -445,9 +433,6 @@
     <t>ReinsurancePortfolio/TestPlans/SupportingData/Template/BP03 BoundPortfolio_ReportOutput_Template.xlsm</t>
   </si>
   <si>
-    <t>PreReq 01  PortfolioMetrics_Driver.xlsm</t>
-  </si>
-  <si>
     <t>TPL-012</t>
   </si>
   <si>
@@ -563,6 +548,69 @@
   </si>
   <si>
     <t>ReinsurancePortfolio/TestPlans/TestOutput/Portfolio/PnL_Comparison_Driver_07282026.xlsm</t>
+  </si>
+  <si>
+    <t>TPL-013</t>
+  </si>
+  <si>
+    <t>TPL-014</t>
+  </si>
+  <si>
+    <t>TPL-015</t>
+  </si>
+  <si>
+    <t>v2.0</t>
+  </si>
+  <si>
+    <t>ReinsurancePortfolio/TestPlans/SupportingData/Template/PreReq_00_AAL_by_Deal_PerilRegion_v2.xlsm</t>
+  </si>
+  <si>
+    <t>PreReq_00_AAL_by_Deal_PerilRegion_v2.xlsm</t>
+  </si>
+  <si>
+    <t>Macro enabled Microsoft excel to extract deal Level AAL and Peril Region AAL for the list of ILS instruments given in the Excel input file and write it to any excel file where the output is required</t>
+  </si>
+  <si>
+    <t>PreReq 01_PortfolioMetrics_Driver.xlsm</t>
+  </si>
+  <si>
+    <t>ReinsurancePortfolio/TestPlans/SupportingData/Template/PreReq 01_PortfolioMetrics_Driver.xlsm</t>
+  </si>
+  <si>
+    <t>Macro enabled Microsoft excel to extract Portfolio Metrics from SQL db for the listed ReportIDs in BoundPortfolio table where Name is Test</t>
+  </si>
+  <si>
+    <t>Macro enabled Microsoft excel to extract deal Level AAL and Peril Region AAL for the list of ILS instruments in ILSData tbale in DB and write it to excel sheet . This also can write Bound Portfolio Detail table info which is PreReq_Trans for Buy/Sell and Pricing</t>
+  </si>
+  <si>
+    <t>TC-004</t>
+  </si>
+  <si>
+    <t>TC-005</t>
+  </si>
+  <si>
+    <t>BuySell_Output_07282026</t>
+  </si>
+  <si>
+    <t>Pricing _Output_07282026</t>
+  </si>
+  <si>
+    <t>18/249 run completed</t>
+  </si>
+  <si>
+    <t>18 show error and need investgiation</t>
+  </si>
+  <si>
+    <t>138/138 Completed</t>
+  </si>
+  <si>
+    <t>All runs Completed</t>
+  </si>
+  <si>
+    <t>ReinsurancePortfolio/TestPlans/TestOutput/Portfolio/BuySell_Output_07282026.xlsb</t>
+  </si>
+  <si>
+    <t>ReinsurancePortfolio/TestPlans/TestOutput/Portfolio/Pricing _Output_07282026.xlsb</t>
   </si>
 </sst>
 </file>
@@ -639,7 +687,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -697,6 +745,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor rgb="FFF3F4F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -996,15 +1056,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1047,23 +1101,29 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="14" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1338,18 +1398,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
     </row>
     <row r="2" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="62"/>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
+      <c r="A2" s="65"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
     </row>
     <row r="3" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="61" t="s">
@@ -1360,60 +1420,60 @@
       <c r="D3" s="61"/>
     </row>
     <row r="4" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="63" t="s">
+      <c r="A4" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="63"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="64" t="s">
+      <c r="B5" s="63" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="64"/>
-      <c r="D5" s="64"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="63"/>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="64" t="s">
+      <c r="B6" s="63" t="s">
         <v>78</v>
       </c>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
+      <c r="C6" s="63"/>
+      <c r="D6" s="63"/>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="65">
+      <c r="B7" s="62">
         <v>46231</v>
       </c>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
+      <c r="C7" s="63"/>
+      <c r="D7" s="63"/>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="64" t="s">
+      <c r="B8" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="63"/>
     </row>
     <row r="10" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="63" t="s">
+      <c r="A10" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="63"/>
-      <c r="C10" s="63"/>
-      <c r="D10" s="63"/>
+      <c r="B10" s="64"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="64"/>
     </row>
     <row r="11" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
@@ -1447,7 +1507,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>79</v>
@@ -1486,12 +1546,12 @@
       <c r="D17" s="4"/>
     </row>
     <row r="19" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="63" t="s">
+      <c r="A19" s="64" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="63"/>
-      <c r="C19" s="63"/>
-      <c r="D19" s="63"/>
+      <c r="B19" s="64"/>
+      <c r="C19" s="64"/>
+      <c r="D19" s="64"/>
     </row>
     <row r="20" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
@@ -1554,12 +1614,12 @@
       <c r="D25" s="3"/>
     </row>
     <row r="27" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="63" t="s">
+      <c r="A27" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="63"/>
-      <c r="C27" s="63"/>
-      <c r="D27" s="63"/>
+      <c r="B27" s="64"/>
+      <c r="C27" s="64"/>
+      <c r="D27" s="64"/>
     </row>
     <row r="28" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
@@ -1584,7 +1644,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B30" s="7">
         <f>COUNTA(SPs!B5:B500)</f>
@@ -1598,8 +1658,8 @@
         <v>14</v>
       </c>
       <c r="B31" s="5">
-        <f>COUNTA(Templates!B5:B504)</f>
-        <v>13</v>
+        <f>COUNTA(Templates!B5:B506)</f>
+        <v>15</v>
       </c>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
@@ -1621,23 +1681,23 @@
       </c>
       <c r="B33" s="5">
         <f>COUNTA(Outcomes!B5:B500)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:D2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="A19:D19"/>
     <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A1:D2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -1646,7 +1706,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -1731,10 +1791,10 @@
         <v>61</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D5" s="29" t="s">
         <v>80</v>
@@ -1760,19 +1820,19 @@
         <v>83</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E6" s="15" t="s">
         <v>48</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G6" s="13" t="s">
         <v>81</v>
@@ -1789,19 +1849,19 @@
         <v>86</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>48</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G7" s="14" t="s">
         <v>81</v>
@@ -1815,13 +1875,13 @@
     </row>
     <row r="8" spans="1:9" s="12" customFormat="1" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="34" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>84</v>
@@ -1844,22 +1904,22 @@
     </row>
     <row r="9" spans="1:9" s="12" customFormat="1" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="34" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>48</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="G9" s="14" t="s">
         <v>81</v>
@@ -1873,22 +1933,22 @@
     </row>
     <row r="10" spans="1:9" s="12" customFormat="1" ht="38.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="36" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B10" s="37" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D10" s="38" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="E10" s="39" t="s">
         <v>48</v>
       </c>
       <c r="F10" s="39" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="G10" s="38" t="s">
         <v>81</v>
@@ -1901,23 +1961,23 @@
       </c>
     </row>
     <row r="11" spans="1:9" s="12" customFormat="1" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="43" t="s">
-        <v>105</v>
-      </c>
-      <c r="B11" s="44" t="s">
-        <v>134</v>
-      </c>
-      <c r="C11" s="44" t="s">
-        <v>100</v>
-      </c>
-      <c r="D11" s="44" t="s">
-        <v>87</v>
+      <c r="A11" s="58" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>176</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>97</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>178</v>
       </c>
       <c r="E11" s="29" t="s">
         <v>48</v>
       </c>
       <c r="F11" s="29" t="s">
-        <v>88</v>
+        <v>177</v>
       </c>
       <c r="G11" s="29" t="s">
         <v>81</v>
@@ -1930,23 +1990,23 @@
       </c>
     </row>
     <row r="12" spans="1:9" s="12" customFormat="1" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="45" t="s">
+      <c r="A12" s="59" t="s">
+        <v>105</v>
+      </c>
+      <c r="B12" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="B12" s="13" t="s">
-        <v>111</v>
-      </c>
       <c r="C12" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>90</v>
+        <v>98</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>175</v>
       </c>
       <c r="E12" s="15" t="s">
         <v>48</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G12" s="13" t="s">
         <v>81</v>
@@ -1958,111 +2018,111 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="46" t="s">
-        <v>118</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>112</v>
+    <row r="13" spans="1:9" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="59" t="s">
+        <v>115</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>174</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>93</v>
+        <v>98</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>179</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>48</v>
+        <v>172</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="G13" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="G13" s="17" t="s">
         <v>81</v>
       </c>
       <c r="H13" s="21">
         <v>46231</v>
       </c>
-      <c r="I13" s="47" t="s">
+      <c r="I13" s="45" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="48" t="s">
-        <v>124</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>113</v>
-      </c>
-      <c r="C14" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="D14" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="E14" s="18" t="s">
+    <row r="14" spans="1:9" s="12" customFormat="1" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="59" t="s">
+        <v>120</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="E14" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="G14" s="22" t="s">
+      <c r="F14" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="G14" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="H14" s="23">
+      <c r="H14" s="16">
         <v>46231</v>
       </c>
-      <c r="I14" s="49" t="s">
+      <c r="I14" s="33" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="48" t="s">
-        <v>125</v>
+    <row r="15" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+      <c r="A15" s="44" t="s">
+        <v>121</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>107</v>
+        <v>100</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>93</v>
       </c>
       <c r="E15" s="17" t="s">
         <v>48</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="G15" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="H15" s="20">
+      <c r="H15" s="21">
         <v>46231</v>
       </c>
-      <c r="I15" s="47" t="s">
+      <c r="I15" s="45" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="48" t="s">
-        <v>125</v>
+    <row r="16" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="46" t="s">
+        <v>130</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="E16" s="18" t="s">
         <v>48</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="G16" s="22" t="s">
         <v>81</v>
@@ -2070,93 +2130,129 @@
       <c r="H16" s="23">
         <v>46231</v>
       </c>
-      <c r="I16" s="49" t="s">
+      <c r="I16" s="47" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="28.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="50" t="s">
-        <v>135</v>
-      </c>
-      <c r="B17" s="51" t="s">
-        <v>120</v>
-      </c>
-      <c r="C17" s="52" t="s">
-        <v>121</v>
-      </c>
-      <c r="D17" s="53" t="s">
-        <v>123</v>
-      </c>
-      <c r="E17" s="51" t="s">
+    <row r="17" spans="1:9" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="46" t="s">
+        <v>169</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="E17" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="F17" s="51" t="s">
+      <c r="F17" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="H17" s="20">
+        <v>46231</v>
+      </c>
+      <c r="I17" s="45" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="46" t="s">
+        <v>170</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="D18" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="G17" s="52" t="s">
+      <c r="E18" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="G18" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="H17" s="54">
+      <c r="H18" s="23">
         <v>46231</v>
       </c>
-      <c r="I17" s="55" t="s">
+      <c r="I18" s="47" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="42"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="42"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
+    <row r="19" spans="1:9" ht="28.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="48" t="s">
+        <v>171</v>
+      </c>
+      <c r="B19" s="49" t="s">
+        <v>145</v>
+      </c>
+      <c r="C19" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="D19" s="51" t="s">
+        <v>119</v>
+      </c>
+      <c r="E19" s="49" t="s">
+        <v>48</v>
+      </c>
+      <c r="F19" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="G19" s="50" t="s">
+        <v>81</v>
+      </c>
+      <c r="H19" s="52">
+        <v>46231</v>
+      </c>
+      <c r="I19" s="53" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
+      <c r="A20" s="42"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
+      <c r="A21" s="17"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
@@ -2290,13 +2386,35 @@
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
     </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="A3:I3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="I5:I34" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="I5:I36" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Not Started,In Progress,Complete,Blocked,N/A"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2385,22 +2503,22 @@
       <c r="A5" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B5" s="56" t="s">
-        <v>146</v>
+      <c r="B5" s="54" t="s">
+        <v>141</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>66</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="G5" s="57">
+      <c r="G5" s="55">
         <v>46231</v>
       </c>
       <c r="H5" s="3" t="s">
@@ -2409,24 +2527,24 @@
     </row>
     <row r="6" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>147</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>152</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>66</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="G6" s="58">
+      <c r="G6" s="56">
         <v>46231</v>
       </c>
       <c r="H6" s="4" t="s">
@@ -2435,24 +2553,24 @@
     </row>
     <row r="7" spans="1:8" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>66</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="G7" s="57">
+      <c r="G7" s="55">
         <v>46231</v>
       </c>
       <c r="H7" s="3" t="s">
@@ -2722,7 +2840,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="60" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B1" s="60"/>
       <c r="C1" s="60"/>
@@ -3152,109 +3270,145 @@
         <v>76</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>158</v>
-      </c>
       <c r="D5" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="H5" s="57">
+        <v>152</v>
+      </c>
+      <c r="H5" s="55">
         <v>46231</v>
       </c>
-      <c r="I5" s="56" t="s">
-        <v>160</v>
+      <c r="I5" s="54" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>171</v>
-      </c>
       <c r="F6" s="4" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="H6" s="58">
+        <v>152</v>
+      </c>
+      <c r="H6" s="56">
         <v>46231</v>
       </c>
-      <c r="I6" s="59" t="s">
-        <v>164</v>
+      <c r="I6" s="57" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>29</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="H7" s="57">
+        <v>158</v>
+      </c>
+      <c r="H7" s="55">
         <v>46231</v>
       </c>
-      <c r="I7" s="56" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="I7" s="54" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="H8" s="56">
+        <v>46253</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="H9" s="55">
+        <v>46253</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
